--- a/光伏配储项目/电价数据/2026/星云站.xlsx
+++ b/光伏配储项目/电价数据/2026/星云站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.60292</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8069299999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.67874</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6084700000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.59149</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.59202</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45089</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44007</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43232</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40632</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40631</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43765</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42461</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39346</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42744</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43158</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42427</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42129</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45627</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5180900000000001</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.20212</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26906</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.21747</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17945</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.20405</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06261</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.24382</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24627</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23077</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.22948</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.92374</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.52764</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.54337</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60407</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.60333</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.72581</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.21134</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39349</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.76056</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65426</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9305800000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.53553</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.2727</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.38608</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.14113</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.23894</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.3467</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.50851</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.51036</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7504299999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.80211</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.30943</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.12345</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8650800000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7934</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75334</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51432</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47654</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46431</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42375</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69973</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74305</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86187</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.90246</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48876</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.50659</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49635</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49654</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47921</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46187</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.6890599999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.54867</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.6494099999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43141</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.40499</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42912</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50942</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.58472</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.85988</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.07532</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.58599</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.9381699999999999</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8922</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.56252</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.84584</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.25629</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05881</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.41052</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50363</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58808</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.54804</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.85903</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60438</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.76854</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.83478</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.20942</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.78889</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15808</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.87573</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.26003</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.16438</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.32322</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.10496</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.14907</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7079</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.03983</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.8930499999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.05008</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9574199999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.07328</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.87715</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44667</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.81496</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8349</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4461</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42572</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44069</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3343</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5020899999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48232</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47963</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44124</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42365</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43846</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46691</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44119</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.18198</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.24809</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.15774</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.5531699999999999</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.49765</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.5830299999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.5898600000000001</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.66908</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.63615</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.9035599999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.59549</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.70566</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.78046</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.86721</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52208</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.52396</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.77646</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.7232000000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64459</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.63785</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.50041</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.59023</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.40989</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38725</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45875</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50375</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.51173</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.61199</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.58112</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6028</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.23212</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.60963</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.73375</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46982</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5106000000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57841</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.71694</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.71687</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.85529</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.45429</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.59709</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45903</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.54713</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.60068</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.72877</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56245</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.8690599999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.69674</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.51583</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6475700000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43684</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45395</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51342</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49118</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43849</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44489</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44229</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.46193</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.46606</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6365700000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.48717</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.9936699999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.59096</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.49067</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39587</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49108</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.6449600000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48141</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45055</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45523</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.4693</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5337999999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6571399999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.51307</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.7086699999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.55388</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50205</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.47801</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.45406</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.43118</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30897</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.40764</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.24639</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.26762</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14544</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.04505</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.2820299999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.24912</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.24008</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.23686</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.19385</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24721</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25407</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22427</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.0866</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.18586</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.15143</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44729</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45399</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.32955</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.44445</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.2431</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28164</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.2087</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.08838</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.21923</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.27813</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.25888</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24009</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.27306</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.22832</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28192</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.25285</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10348</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04401</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01134</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20874</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05053</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19435</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.20211</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.03227</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06288000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0611</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32295</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.29997</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78492</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87102</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.70268</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.59008</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41929</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41119</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5003</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5587300000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.64923</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8687699999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.4913</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.69036</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.44733</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8326699999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.48498</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27862</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.49868</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.48443</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.22905</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33449</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9045299999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28076</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23934</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.40771</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27283</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1945</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29824</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.28986</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.24277</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.26328</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24849</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26771</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28249</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.39934</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.81172</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.38461</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08569</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.65388</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7428400000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6071</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46429</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.46777</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.22841</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46083</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.04339</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24356</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02938</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25448</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24551</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27812</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.26832</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.48158</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.66242</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.27124</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.27911</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.27678</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.21918</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.23234</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.23872</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.22782</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.23532</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.20984</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.25425</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.27156</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.20177</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.20231</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.27936</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.08716</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.22149</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.26181</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.08804000000000001</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.24645</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.25942</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.2457</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.21759</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.15505</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.19947</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22007</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.27105</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.26904</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23774</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.24008</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.24162</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.24826</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.22274</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.22525</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26928</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.2415</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.24205</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26746</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27895</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.25065</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22123</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.23797</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.24049</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.22737</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26388</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.24147</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42572</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30584</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.39457</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27829</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23759</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.44434</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.50344</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32515</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.43527</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.2197</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.46671</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.7440399999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.43898</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.54926</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5287000000000001</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.42691</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.49732</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.56712</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.44196</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.48573</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.43581</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.6585599999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.41647</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.50083</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.8304</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.5670499999999999</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.5342899999999999</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.5015500000000001</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.48777</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.66279</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.50869</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.53038</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.46805</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.5509299999999999</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.45251</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.68891</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.5111600000000001</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.50736</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.48501</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.46668</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7452799999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.46288</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49002</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22299</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28079</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.13942</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.24541</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.24124</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.24361</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.24064</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.21571</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.24037</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.24568</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.25609</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.25551</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.23279</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.22169</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.26923</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29178</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26359</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28024</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.29397</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.25778</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.22732</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33037</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.11864</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.30719</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37286</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43235</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.63951</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8233200000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.31388</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.47653</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.38404</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.48464</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.43967</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.44047</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.47977</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.6160399999999999</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.56121</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6951900000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6526900000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.72454</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.43025</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.84676</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.44136</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.67169</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.5721799999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.53854</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.44939</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.52771</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.40975</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33066</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47287</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.46623</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.50064</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.53753</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.6065900000000001</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.6165</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43064</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.43735</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.68588</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.86621</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.45655</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.45729</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.50404</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.59136</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.43926</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.5131599999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.49075</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.44088</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.52227</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75444</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60645</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65325</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43168</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.40598</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.37126</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.40893</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.13347</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.5204500000000001</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.08923</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.40388</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.40511</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46158</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.44167</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46276</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.45655</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.24517</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27835</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.26764</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.27434</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.27315</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.24927</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.22948</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.25972</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.26081</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.23648</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.27603</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.23255</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.13392</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.12489</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.12398</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.23292</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.11803</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.25258</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.23185</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.21932</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.22533</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.24781</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.22215</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.22921</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.23275</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.09762</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.24692</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.23074</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.20954</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.08896</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11247</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27387</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24635</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.01518</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.18408</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.27212</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01591</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28647</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.25017</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28313</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.24988</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25409</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27613</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2542</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.27519</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.24229</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25148</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.22751</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.22639</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.26862</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.14612</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.23432</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.23068</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.24079</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25558</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.24925</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.13146</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.09595000000000001</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.10472</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.10471</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.10402</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23586</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.09401000000000001</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.10316</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22433</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.09601999999999999</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.09593</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.10734</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.06889000000000001</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25497</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.11191</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00186</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14135</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02184</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01604</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04085</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02933</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00099</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02248</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03639</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19961</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26434</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27766</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.10583</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.2984</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5211</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.46842</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.20238</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.23934</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.23124</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23632</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23288</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.10893</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22822</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21381</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.11275</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.07504000000000001</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.09145</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.10246</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.11615</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.08131999999999999</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.12819</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.13471</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.14666</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42516</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.26913</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.10209</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.26387</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.5531</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.86734</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85905</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10651</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.09505</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27191</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27471</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.16935</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.14323</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28428</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00111</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28486</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00065</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06670999999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47349</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.07514</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.65626</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.55098</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.59194</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.06735</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9731799999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.56012</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.72114</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.6071299999999999</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83004</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82826</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8325399999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93031</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.5488999999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6031599999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.55669</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33319</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.4634</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.23894</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.43389</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48178</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.26659</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26277</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.25661</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.23514</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.25131</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.22796</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.23138</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.10892</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.24257</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.25443</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.55501</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.48495</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.40581</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32119</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40079</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.47522</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.7039099999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.45305</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46142</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.47239</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.53288</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.44358</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47059</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.6916599999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8486</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.10284</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.48188</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.55492</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5727300000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.01153</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.88501</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5301399999999999</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.64227</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.48452</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.45816</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.42605</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.45388</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22269</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.33952</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4347200000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43477</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50369</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.58678</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.23192</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.00989</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.64693</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51627</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.64102</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5783200000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45621</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.73545</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.98262</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.8863099999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7963300000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.72013</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.41689</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46715</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34399</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.13438</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.46044</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.43841</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.48826</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.7612899999999999</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.46665</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.21423</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.54863</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.44515</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.76095</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.47157</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.40618</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.47983</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.44327</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.52336</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.6557500000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.5130399999999999</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42998</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47963</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.64407</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47551</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.48909</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3498</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.90274</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.46961</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.52477</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.49522</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.47171</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.50457</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42178</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.49897</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.57804</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.46658</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.45679</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.44629</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35115</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17584</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14551</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1983</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14334</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04583</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12085</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22491</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26154</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14719</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19172</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22647</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26027</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15167</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15414</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19577</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14034</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28329</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.49422</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.43141</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.5354099999999999</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45442</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37853</v>
       </c>
     </row>
   </sheetData>
